--- a/NBFC-MF/Borrowers/Shantibala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Shantibala_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>16200</v>
+        <v>14700</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>14295.302542559919</v>
+        <v>13117.062707143943</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>5704.6974574400811</v>
+        <v>6882.937292856057</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1637,143 +1637,153 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A28" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B28" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="4" t="str">
+      <c r="D28" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E28" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E28" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="str">
+        <v>66.53542602221556</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="5"/>
+        <v>233.46457397778443</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="4"/>
+        <v>14061.837968582135</v>
+      </c>
+      <c r="H28" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5938.1620314178654</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A29" s="19">
+        <v>46282</v>
+      </c>
+      <c r="B29" s="24">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="21" t="str">
+      <c r="D29" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E29" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E29" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F29" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G29" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H29" s="21" t="str">
+        <v>65.44879880012914</v>
+      </c>
+      <c r="F29" s="21">
+        <f t="shared" si="5"/>
+        <v>234.55120119987086</v>
+      </c>
+      <c r="G29" s="21">
+        <f t="shared" si="4"/>
+        <v>13827.286767382264</v>
+      </c>
+      <c r="H29" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6172.7132326177361</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A30" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B30" s="23">
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="4" t="str">
+      <c r="D30" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E30" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E30" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="str">
+        <v>64.357114028198367</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="5"/>
+        <v>235.64288597180163</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>13591.643881410462</v>
+      </c>
+      <c r="H30" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6408.3561185895378</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A31" s="19">
+        <v>46282</v>
+      </c>
+      <c r="B31" s="24">
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="C31" s="20"/>
-      <c r="D31" s="21" t="str">
+      <c r="D31" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E31" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E31" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F31" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G31" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H31" s="21" t="str">
+        <v>63.260348166786208</v>
+      </c>
+      <c r="F31" s="21">
+        <f t="shared" si="5"/>
+        <v>236.7396518332138</v>
+      </c>
+      <c r="G31" s="21">
+        <f t="shared" si="4"/>
+        <v>13354.904229577249</v>
+      </c>
+      <c r="H31" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6645.0957704227512</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A32" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B32" s="23">
+        <f t="shared" si="3"/>
+        <v>31</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="4" t="str">
+      <c r="D32" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E32" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E32" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="str">
+        <v>62.15847756669374</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="5"/>
+        <v>237.84152243330627</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="4"/>
+        <v>13117.062707143943</v>
+      </c>
+      <c r="H32" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>6882.937292856057</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Shantibala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Shantibala_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>14700</v>
+        <v>14100</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>13117.062707143943</v>
+        <v>12638.053512615395</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6882.937292856057</v>
+        <v>7361.9464873846046</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1787,59 +1787,63 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A33" s="19">
+        <v>46288</v>
+      </c>
+      <c r="B33" s="24">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="C33" s="20"/>
-      <c r="D33" s="21" t="str">
+      <c r="D33" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E33" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E33" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G33" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H33" s="21" t="str">
+        <v>61.051478468650274</v>
+      </c>
+      <c r="F33" s="21">
+        <f t="shared" si="5"/>
+        <v>238.94852153134974</v>
+      </c>
+      <c r="G33" s="21">
+        <f t="shared" si="4"/>
+        <v>12878.114185612594</v>
+      </c>
+      <c r="H33" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>7121.8858143874058</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A34" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B34" s="23">
+        <f t="shared" si="3"/>
+        <v>33</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="4" t="str">
+      <c r="D34" s="4">
         <f t="shared" ref="D34:D65" si="6">IF(AND($A34&lt;&gt;"",$B34&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E34" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F34" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G34" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H34" s="4" t="str">
+        <v>59.939327002801001</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="5"/>
+        <v>240.06067299719899</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="4"/>
+        <v>12638.053512615395</v>
+      </c>
+      <c r="H34" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>7361.9464873846046</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Shantibala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Shantibala_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>14100</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>12638.053512615395</v>
+        <v>12154.574982735843</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>7361.9464873846046</v>
+        <v>7845.4250172641568</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1847,59 +1847,63 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A35" s="19">
+        <v>46297</v>
+      </c>
+      <c r="B35" s="24">
+        <f t="shared" si="3"/>
+        <v>34</v>
       </c>
       <c r="C35" s="20"/>
-      <c r="D35" s="21" t="str">
+      <c r="D35" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E35" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E35" s="21">
         <f t="shared" ref="E35:E66" si="7">IF(AND($A35&lt;&gt;"",$B35&lt;&gt;""),G34*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G35" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H35" s="21" t="str">
+        <v>58.821999188192322</v>
+      </c>
+      <c r="F35" s="21">
+        <f t="shared" si="5"/>
+        <v>241.17800081180769</v>
+      </c>
+      <c r="G35" s="21">
+        <f t="shared" si="4"/>
+        <v>12396.875511803588</v>
+      </c>
+      <c r="H35" s="21">
         <f t="shared" ref="H35:H66" si="8">IF(AND($A35&lt;&gt;"",$B35&lt;&gt;""),$K$7-G35,"")</f>
-        <v/>
+        <v>7603.1244881964121</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A36" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B36" s="23">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="4" t="str">
+      <c r="D36" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E36" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E36" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F36" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G36" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H36" s="4" t="str">
+        <v>57.699470932254741</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="5"/>
+        <v>242.30052906774526</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="4"/>
+        <v>12154.574982735843</v>
+      </c>
+      <c r="H36" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>7845.4250172641568</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
